--- a/data/WP17/WP17_sachgebiete_SPD.xlsx
+++ b/data/WP17/WP17_sachgebiete_SPD.xlsx
@@ -869,7 +869,7 @@
         <v>249</v>
       </c>
       <c r="D5" t="n">
-        <v>27.2495108639687</v>
+        <v>27.2449799196787</v>
       </c>
       <c r="E5" t="n">
         <v>97</v>
@@ -1019,10 +1019,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" t="n">
-        <v>31.7846153846154</v>
+        <v>31.7480916030534</v>
       </c>
       <c r="E14" t="n">
         <v>82</v>
@@ -1277,10 +1277,10 @@
         <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>32.2222222222222</v>
+        <v>32.1333333333333</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
@@ -3506,13 +3506,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{995A72BE-A8BB-40E9-854A-1B9A61760388}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFB119AB-75C3-4CD5-BACC-021E44DD4AFB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94B0B056-1FE4-4DA5-9BE0-85507F70C88D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35757549-868C-4968-B02D-95A426D61514}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7953A18-5FF1-4156-8104-89C6E2924A5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4F3D24E-3A01-443B-853B-4B48C9C291DA}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_SPD.xlsx
+++ b/data/WP17/WP17_sachgebiete_SPD.xlsx
@@ -446,7 +446,7 @@
         <v>34.6196868008949</v>
       </c>
       <c r="E2" t="n">
-        <v>274</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         <v>31.7723342939481</v>
       </c>
       <c r="E3" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         <v>34.2888888888889</v>
       </c>
       <c r="E4" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         <v>26.8393574297189</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>30.855421686747</v>
       </c>
       <c r="E6" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>30.0720720720721</v>
       </c>
       <c r="E7" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
@@ -548,7 +548,7 @@
         <v>30.3300970873786</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +565,7 @@
         <v>30.5414634146341</v>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
         <v>30.4350282485876</v>
       </c>
       <c r="E10" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>38.8978102189781</v>
       </c>
       <c r="E11" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
@@ -616,7 +616,7 @@
         <v>32.6148148148148</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +633,7 @@
         <v>32.7045454545455</v>
       </c>
       <c r="E13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +650,7 @@
         <v>31.2519083969466</v>
       </c>
       <c r="E14" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         <v>31.2231404958678</v>
       </c>
       <c r="E15" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16">
@@ -684,7 +684,7 @@
         <v>35.979381443299</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -701,7 +701,7 @@
         <v>29.7654320987654</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
@@ -718,7 +718,7 @@
         <v>31.4931506849315</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>29.7083333333333</v>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -752,7 +752,7 @@
         <v>32.4507042253521</v>
       </c>
       <c r="E20" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -769,7 +769,7 @@
         <v>29.9857142857143</v>
       </c>
       <c r="E21" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1006,13 +1006,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5A0FDAF-A2CE-43A3-8A39-43D160C8E294}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E8D7D7E-6A85-4E13-8EC3-A0715DA07B9F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F358F76D-2A91-49E2-8DDC-C0B0D76A4D10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{096C9D9D-3669-4FC4-8BEC-77231BDAB720}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFE9017-EDAA-4839-AAEF-6188EF87F893}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D934A5-41CF-4941-9280-E921BE6F26ED}"/>
 </file>